--- a/data/industry/CFM/Channel SSD.xlsx
+++ b/data/industry/CFM/Channel SSD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0FB04F-A19D-423B-A957-778E6E30C19A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D19BBC-9FB3-451B-975D-D7686321437A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Channel SSD 120GB SATA" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -1103,7 +1103,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -1116,6 +1116,121 @@
       </c>
       <c r="G28" s="12">
         <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>23</v>
+      </c>
+      <c r="F29" s="12">
+        <v>24.7</v>
+      </c>
+      <c r="G29" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>23</v>
+      </c>
+      <c r="F30" s="12">
+        <v>24.7</v>
+      </c>
+      <c r="G30" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>23</v>
+      </c>
+      <c r="F31" s="12">
+        <v>24.7</v>
+      </c>
+      <c r="G31" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>23</v>
+      </c>
+      <c r="F32" s="12">
+        <v>24.7</v>
+      </c>
+      <c r="G32" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>25</v>
+      </c>
+      <c r="F33" s="12">
+        <v>26.7</v>
+      </c>
+      <c r="G33" s="12">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1126,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A82D123-E18C-4733-B397-9C03328A1E65}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -1767,7 +1882,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -1780,6 +1895,121 @@
       </c>
       <c r="G28" s="14">
         <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>45</v>
+      </c>
+      <c r="F29" s="14">
+        <v>48</v>
+      </c>
+      <c r="G29" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>45</v>
+      </c>
+      <c r="F30" s="14">
+        <v>48</v>
+      </c>
+      <c r="G30" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>45</v>
+      </c>
+      <c r="F31" s="14">
+        <v>48</v>
+      </c>
+      <c r="G31" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>45</v>
+      </c>
+      <c r="F32" s="14">
+        <v>48</v>
+      </c>
+      <c r="G32" s="14">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>50</v>
+      </c>
+      <c r="F33" s="14">
+        <v>53</v>
+      </c>
+      <c r="G33" s="14">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1790,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DEEDA6-23E7-43DF-BF44-327B2DB18A4F}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -2431,7 +2661,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -2444,6 +2674,121 @@
       </c>
       <c r="G28" s="12">
         <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>77.5</v>
+      </c>
+      <c r="F29" s="12">
+        <v>81</v>
+      </c>
+      <c r="G29" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>77.5</v>
+      </c>
+      <c r="F30" s="12">
+        <v>81</v>
+      </c>
+      <c r="G30" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>77.5</v>
+      </c>
+      <c r="F31" s="12">
+        <v>81</v>
+      </c>
+      <c r="G31" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>77.5</v>
+      </c>
+      <c r="F32" s="12">
+        <v>81</v>
+      </c>
+      <c r="G32" s="12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>87.5</v>
+      </c>
+      <c r="F33" s="12">
+        <v>91</v>
+      </c>
+      <c r="G33" s="12">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2454,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F96F38-689A-4B46-8DFA-A4944FA7A43B}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -3095,7 +3440,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -3108,6 +3453,121 @@
       </c>
       <c r="G28" s="9">
         <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="9">
+        <v>46</v>
+      </c>
+      <c r="F29" s="9">
+        <v>48</v>
+      </c>
+      <c r="G29" s="9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="9">
+        <v>46</v>
+      </c>
+      <c r="F30" s="9">
+        <v>48</v>
+      </c>
+      <c r="G30" s="9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="9">
+        <v>46</v>
+      </c>
+      <c r="F31" s="9">
+        <v>48</v>
+      </c>
+      <c r="G31" s="9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="9">
+        <v>46</v>
+      </c>
+      <c r="F32" s="9">
+        <v>48</v>
+      </c>
+      <c r="G32" s="9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="9">
+        <v>54</v>
+      </c>
+      <c r="F33" s="9">
+        <v>56</v>
+      </c>
+      <c r="G33" s="9">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3118,7 +3578,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAF9F8A-7AB5-472F-A579-46036402780F}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -3759,7 +4219,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -3772,6 +4232,121 @@
       </c>
       <c r="G28" s="12">
         <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>85</v>
+      </c>
+      <c r="F29" s="12">
+        <v>87.2</v>
+      </c>
+      <c r="G29" s="12">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>85</v>
+      </c>
+      <c r="F30" s="12">
+        <v>87.2</v>
+      </c>
+      <c r="G30" s="12">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>85</v>
+      </c>
+      <c r="F31" s="12">
+        <v>87.2</v>
+      </c>
+      <c r="G31" s="12">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>85</v>
+      </c>
+      <c r="F32" s="12">
+        <v>87.2</v>
+      </c>
+      <c r="G32" s="12">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>104</v>
+      </c>
+      <c r="F33" s="12">
+        <v>106.2</v>
+      </c>
+      <c r="G33" s="12">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3782,15 +4357,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F1A6FD-F375-4FB8-8C30-C4A005067594}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="14"/>
+    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -3807,13 +4382,13 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3830,13 +4405,13 @@
       <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="14">
         <v>40.799999999999997</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="14">
         <v>42.8</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="14">
         <v>41.6</v>
       </c>
     </row>
@@ -3853,13 +4428,13 @@
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="14">
         <v>40.799999999999997</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="14">
         <v>42.8</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="14">
         <v>41.6</v>
       </c>
     </row>
@@ -3876,13 +4451,13 @@
       <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="14">
         <v>40.799999999999997</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="14">
         <v>42.8</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="14">
         <v>41.6</v>
       </c>
     </row>
@@ -3899,13 +4474,13 @@
       <c r="D5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="14">
         <v>40.799999999999997</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="14">
         <v>42.8</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="14">
         <v>41.6</v>
       </c>
     </row>
@@ -3922,13 +4497,13 @@
       <c r="D6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="14">
         <v>40.799999999999997</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="14">
         <v>42.8</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="14">
         <v>41.6</v>
       </c>
     </row>
@@ -3945,13 +4520,13 @@
       <c r="D7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="14">
         <v>40.799999999999997</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="14">
         <v>42.8</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="14">
         <v>41.6</v>
       </c>
     </row>
@@ -3968,13 +4543,13 @@
       <c r="D8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="14">
         <v>40.799999999999997</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="14">
         <v>42.8</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="14">
         <v>41.6</v>
       </c>
     </row>
@@ -3991,13 +4566,13 @@
       <c r="D9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="14">
         <v>40.799999999999997</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="14">
         <v>42.8</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="14">
         <v>41.6</v>
       </c>
     </row>
@@ -4014,13 +4589,13 @@
       <c r="D10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="14">
         <v>41.2</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="14">
         <v>43.2</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="14">
         <v>42</v>
       </c>
     </row>
@@ -4037,13 +4612,13 @@
       <c r="D11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="14">
         <v>41.2</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="14">
         <v>43.2</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="14">
         <v>42</v>
       </c>
     </row>
@@ -4060,13 +4635,13 @@
       <c r="D12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="14">
         <v>41.2</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="14">
         <v>43.2</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="14">
         <v>42</v>
       </c>
     </row>
@@ -4083,13 +4658,13 @@
       <c r="D13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="14">
         <v>49.2</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="14">
         <v>51.2</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="14">
         <v>50</v>
       </c>
     </row>
@@ -4106,13 +4681,13 @@
       <c r="D14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="14">
         <v>49.2</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="14">
         <v>51.2</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="14">
         <v>50</v>
       </c>
     </row>
@@ -4129,13 +4704,13 @@
       <c r="D15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="14">
         <v>57.2</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="14">
         <v>59.2</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="14">
         <v>58</v>
       </c>
     </row>
@@ -4152,13 +4727,13 @@
       <c r="D16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="14">
         <v>57.2</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="14">
         <v>59.2</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="14">
         <v>58</v>
       </c>
     </row>
@@ -4175,13 +4750,13 @@
       <c r="D17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="14">
         <v>57.2</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="14">
         <v>59.2</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="14">
         <v>58</v>
       </c>
     </row>
@@ -4198,13 +4773,13 @@
       <c r="D18" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="14">
         <v>57.2</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="14">
         <v>59.2</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="14">
         <v>58</v>
       </c>
     </row>
@@ -4221,13 +4796,13 @@
       <c r="D19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="14">
         <v>74.2</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="14">
         <v>76.2</v>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="14">
         <v>75</v>
       </c>
     </row>
@@ -4244,13 +4819,13 @@
       <c r="D20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="14">
         <v>94.2</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="14">
         <v>96.2</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="14">
         <v>95</v>
       </c>
     </row>
@@ -4267,13 +4842,13 @@
       <c r="D21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="14">
         <v>107.2</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="14">
         <v>109.2</v>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="14">
         <v>108</v>
       </c>
     </row>
@@ -4290,13 +4865,13 @@
       <c r="D22" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="14">
         <v>107.2</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="14">
         <v>109.2</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="14">
         <v>108</v>
       </c>
     </row>
@@ -4313,13 +4888,13 @@
       <c r="D23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="14">
         <v>107.2</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="14">
         <v>109.2</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="14">
         <v>108</v>
       </c>
     </row>
@@ -4336,13 +4911,13 @@
       <c r="D24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="14">
         <v>107.2</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="14">
         <v>109.2</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="14">
         <v>108</v>
       </c>
     </row>
@@ -4359,13 +4934,13 @@
       <c r="D25" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="14">
         <v>109</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="14">
         <v>111</v>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="14">
         <v>110</v>
       </c>
     </row>
@@ -4382,13 +4957,13 @@
       <c r="D26" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="14">
         <v>109</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="14">
         <v>111</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="14">
         <v>110</v>
       </c>
     </row>
@@ -4405,13 +4980,13 @@
       <c r="D27" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="14">
         <v>129</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="14">
         <v>131</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="14">
         <v>130</v>
       </c>
     </row>
@@ -4423,19 +4998,134 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="14">
         <v>139</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="14">
         <v>141</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="14">
         <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="14">
+        <v>139</v>
+      </c>
+      <c r="F29" s="14">
+        <v>141</v>
+      </c>
+      <c r="G29" s="14">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="14">
+        <v>139</v>
+      </c>
+      <c r="F30" s="14">
+        <v>141</v>
+      </c>
+      <c r="G30" s="14">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="14">
+        <v>139</v>
+      </c>
+      <c r="F31" s="14">
+        <v>141</v>
+      </c>
+      <c r="G31" s="14">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="14">
+        <v>139</v>
+      </c>
+      <c r="F32" s="14">
+        <v>141</v>
+      </c>
+      <c r="G32" s="14">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="14">
+        <v>159</v>
+      </c>
+      <c r="F33" s="14">
+        <v>161</v>
+      </c>
+      <c r="G33" s="14">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -4446,7 +5136,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F720D88E-37F2-4EF2-B2CA-01688ACF7295}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -5087,7 +5777,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -5100,6 +5790,121 @@
       </c>
       <c r="G28" s="12">
         <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>87</v>
+      </c>
+      <c r="F29" s="12">
+        <v>89</v>
+      </c>
+      <c r="G29" s="12">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>87</v>
+      </c>
+      <c r="F30" s="12">
+        <v>89</v>
+      </c>
+      <c r="G30" s="12">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>87</v>
+      </c>
+      <c r="F31" s="12">
+        <v>89</v>
+      </c>
+      <c r="G31" s="12">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>87</v>
+      </c>
+      <c r="F32" s="12">
+        <v>89</v>
+      </c>
+      <c r="G32" s="12">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>99</v>
+      </c>
+      <c r="F33" s="12">
+        <v>101</v>
+      </c>
+      <c r="G33" s="12">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5110,7 +5915,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD5A656-5B30-45CF-B579-A97C69E643A5}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -5751,7 +6556,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -5764,6 +6569,121 @@
       </c>
       <c r="G28" s="12">
         <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>144</v>
+      </c>
+      <c r="F29" s="12">
+        <v>146</v>
+      </c>
+      <c r="G29" s="12">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>144</v>
+      </c>
+      <c r="F30" s="12">
+        <v>146</v>
+      </c>
+      <c r="G30" s="12">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>144</v>
+      </c>
+      <c r="F31" s="12">
+        <v>146</v>
+      </c>
+      <c r="G31" s="12">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>144</v>
+      </c>
+      <c r="F32" s="12">
+        <v>146</v>
+      </c>
+      <c r="G32" s="12">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>169</v>
+      </c>
+      <c r="F33" s="12">
+        <v>171</v>
+      </c>
+      <c r="G33" s="12">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -5774,7 +6694,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3EDF89-A497-4D9B-AE60-D1EDE4F7FB0B}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -6415,7 +7335,7 @@
         <v>46049</v>
       </c>
       <c r="C28" s="7">
-        <v>0.45833333333333298</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>8</v>
@@ -6428,6 +7348,121 @@
       </c>
       <c r="G28" s="12">
         <v>260</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="12">
+        <v>257</v>
+      </c>
+      <c r="F29" s="12">
+        <v>264</v>
+      </c>
+      <c r="G29" s="12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="12">
+        <v>257</v>
+      </c>
+      <c r="F30" s="12">
+        <v>264</v>
+      </c>
+      <c r="G30" s="12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="12">
+        <v>257</v>
+      </c>
+      <c r="F31" s="12">
+        <v>264</v>
+      </c>
+      <c r="G31" s="12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="12">
+        <v>257</v>
+      </c>
+      <c r="F32" s="12">
+        <v>264</v>
+      </c>
+      <c r="G32" s="12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="10">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="12">
+        <v>297</v>
+      </c>
+      <c r="F33" s="12">
+        <v>304</v>
+      </c>
+      <c r="G33" s="12">
+        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/CFM/Channel SSD.xlsx
+++ b/data/industry/CFM/Channel SSD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B078B7-00DE-44C8-9263-F666EAD144A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB74AD9C-A433-4803-97EC-3AB281F5D545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -74,26 +74,27 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  <numFmts count="7">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -106,7 +107,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -137,49 +138,53 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -462,19 +467,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,7 +502,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -520,7 +525,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -543,7 +548,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -566,7 +571,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -589,7 +594,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -612,7 +617,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -635,7 +640,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -658,7 +663,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -681,7 +686,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -704,7 +709,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -727,7 +732,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -750,7 +755,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -773,7 +778,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -796,7 +801,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -819,7 +824,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -842,7 +847,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -865,7 +870,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -888,7 +893,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -911,7 +916,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -934,7 +939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -957,7 +962,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -980,7 +985,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -1003,7 +1008,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1026,7 +1031,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1049,7 +1054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1072,7 +1077,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1095,7 +1100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1118,7 +1123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1141,7 +1146,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1164,7 +1169,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1187,7 +1192,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1210,7 +1215,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1233,7 +1238,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1256,7 +1261,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1279,7 +1284,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1302,7 +1307,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1325,7 +1330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1348,7 +1353,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1369,6 +1374,144 @@
       </c>
       <c r="G39" s="12">
         <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>17</v>
+      </c>
+      <c r="F40" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="G40" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>17</v>
+      </c>
+      <c r="F41" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="G41" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>17</v>
+      </c>
+      <c r="F42" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="G42" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>17</v>
+      </c>
+      <c r="F43" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="G43" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>17</v>
+      </c>
+      <c r="F44" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="G44" s="12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>17</v>
+      </c>
+      <c r="F45" s="12">
+        <v>18.7</v>
+      </c>
+      <c r="G45" s="12">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1379,19 +1522,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A82D123-E18C-4733-B397-9C03328A1E65}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1414,7 +1557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1437,7 +1580,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1460,7 +1603,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1483,7 +1626,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1506,7 +1649,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1529,7 +1672,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1552,7 +1695,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1575,7 +1718,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1598,7 +1741,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1621,7 +1764,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1644,7 +1787,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1667,7 +1810,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -1690,7 +1833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -1713,7 +1856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -1736,7 +1879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -1759,7 +1902,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -1782,7 +1925,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -1805,7 +1948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -1828,7 +1971,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -1851,7 +1994,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -1874,7 +2017,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -1897,7 +2040,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -1920,7 +2063,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1943,7 +2086,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1966,7 +2109,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1989,7 +2132,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2012,7 +2155,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2035,7 +2178,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2058,7 +2201,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2081,7 +2224,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2104,7 +2247,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2127,7 +2270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2150,7 +2293,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2173,7 +2316,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2196,7 +2339,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2219,7 +2362,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2242,7 +2385,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2265,7 +2408,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2286,6 +2429,144 @@
       </c>
       <c r="G39" s="14">
         <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="14">
+        <v>38</v>
+      </c>
+      <c r="F40" s="14">
+        <v>41</v>
+      </c>
+      <c r="G40" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="14">
+        <v>37</v>
+      </c>
+      <c r="F41" s="14">
+        <v>40</v>
+      </c>
+      <c r="G41" s="14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="14">
+        <v>36</v>
+      </c>
+      <c r="F42" s="14">
+        <v>39</v>
+      </c>
+      <c r="G42" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="14">
+        <v>36</v>
+      </c>
+      <c r="F43" s="14">
+        <v>39</v>
+      </c>
+      <c r="G43" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="14">
+        <v>36</v>
+      </c>
+      <c r="F44" s="14">
+        <v>39</v>
+      </c>
+      <c r="G44" s="14">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="14">
+        <v>36</v>
+      </c>
+      <c r="F45" s="14">
+        <v>39</v>
+      </c>
+      <c r="G45" s="14">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2296,19 +2577,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DEEDA6-23E7-43DF-BF44-327B2DB18A4F}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2331,7 +2612,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2354,7 +2635,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -2377,7 +2658,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -2400,7 +2681,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -2423,7 +2704,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -2446,7 +2727,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -2469,7 +2750,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -2492,7 +2773,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -2515,7 +2796,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -2538,7 +2819,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -2561,7 +2842,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -2584,7 +2865,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2607,7 +2888,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2630,7 +2911,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2653,7 +2934,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2676,7 +2957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2699,7 +2980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2722,7 +3003,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2745,7 +3026,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2768,7 +3049,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2791,7 +3072,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2814,7 +3095,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2837,7 +3118,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2860,7 +3141,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2883,7 +3164,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2906,7 +3187,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2929,7 +3210,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2952,7 +3233,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2975,7 +3256,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2998,7 +3279,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3021,7 +3302,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3044,7 +3325,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3067,7 +3348,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3090,7 +3371,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3113,7 +3394,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3136,7 +3417,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3159,7 +3440,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3182,7 +3463,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3203,6 +3484,144 @@
       </c>
       <c r="G39" s="12">
         <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>72.5</v>
+      </c>
+      <c r="F40" s="12">
+        <v>76</v>
+      </c>
+      <c r="G40" s="12">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>69.5</v>
+      </c>
+      <c r="F41" s="12">
+        <v>73</v>
+      </c>
+      <c r="G41" s="12">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>67.5</v>
+      </c>
+      <c r="F42" s="12">
+        <v>71</v>
+      </c>
+      <c r="G42" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>67.5</v>
+      </c>
+      <c r="F43" s="12">
+        <v>71</v>
+      </c>
+      <c r="G43" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>67.5</v>
+      </c>
+      <c r="F44" s="12">
+        <v>71</v>
+      </c>
+      <c r="G44" s="12">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>67.5</v>
+      </c>
+      <c r="F45" s="12">
+        <v>71</v>
+      </c>
+      <c r="G45" s="12">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -3213,19 +3632,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F96F38-689A-4B46-8DFA-A4944FA7A43B}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3248,7 +3667,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -3271,7 +3690,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3294,7 +3713,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3317,7 +3736,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3340,7 +3759,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3363,7 +3782,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3386,7 +3805,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3409,7 +3828,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3432,7 +3851,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3455,7 +3874,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3478,7 +3897,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3501,7 +3920,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3524,7 +3943,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3547,7 +3966,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3570,7 +3989,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3593,7 +4012,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3616,7 +4035,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3639,7 +4058,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3662,7 +4081,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3685,7 +4104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3708,7 +4127,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3731,7 +4150,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3754,7 +4173,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3777,7 +4196,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3800,7 +4219,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3823,7 +4242,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3846,7 +4265,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3869,7 +4288,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3892,7 +4311,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3915,7 +4334,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3938,7 +4357,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3961,7 +4380,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3984,7 +4403,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4007,7 +4426,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4030,7 +4449,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4053,7 +4472,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4076,7 +4495,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -4099,7 +4518,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -4120,6 +4539,144 @@
       </c>
       <c r="G39" s="9">
         <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="9">
+        <v>41</v>
+      </c>
+      <c r="F40" s="9">
+        <v>43</v>
+      </c>
+      <c r="G40" s="9">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="9">
+        <v>40</v>
+      </c>
+      <c r="F41" s="9">
+        <v>42</v>
+      </c>
+      <c r="G41" s="9">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="9">
+        <v>40</v>
+      </c>
+      <c r="F42" s="9">
+        <v>42</v>
+      </c>
+      <c r="G42" s="9">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="9">
+        <v>40</v>
+      </c>
+      <c r="F43" s="9">
+        <v>42</v>
+      </c>
+      <c r="G43" s="9">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="9">
+        <v>40</v>
+      </c>
+      <c r="F44" s="9">
+        <v>42</v>
+      </c>
+      <c r="G44" s="9">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="9">
+        <v>40</v>
+      </c>
+      <c r="F45" s="9">
+        <v>42</v>
+      </c>
+      <c r="G45" s="9">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -4130,19 +4687,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAF9F8A-7AB5-472F-A579-46036402780F}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4165,7 +4722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4188,7 +4745,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4211,7 +4768,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4234,7 +4791,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4257,7 +4814,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4280,7 +4837,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4303,7 +4860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4326,7 +4883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4349,7 +4906,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4372,7 +4929,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4395,7 +4952,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4418,7 +4975,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4441,7 +4998,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4464,7 +5021,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4487,7 +5044,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4510,7 +5067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4533,7 +5090,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4556,7 +5113,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4579,7 +5136,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4602,7 +5159,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4625,7 +5182,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4648,7 +5205,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4671,7 +5228,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4694,7 +5251,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4717,7 +5274,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4740,7 +5297,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4763,7 +5320,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4786,7 +5343,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4809,7 +5366,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4832,7 +5389,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4855,7 +5412,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4878,7 +5435,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4901,7 +5458,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4924,7 +5481,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4947,7 +5504,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -4970,7 +5527,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -4993,7 +5550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5016,7 +5573,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5037,6 +5594,144 @@
       </c>
       <c r="G39" s="12">
         <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>84</v>
+      </c>
+      <c r="F40" s="12">
+        <v>86</v>
+      </c>
+      <c r="G40" s="12">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>81</v>
+      </c>
+      <c r="F41" s="12">
+        <v>83</v>
+      </c>
+      <c r="G41" s="12">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>81</v>
+      </c>
+      <c r="F42" s="12">
+        <v>83</v>
+      </c>
+      <c r="G42" s="12">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>81</v>
+      </c>
+      <c r="F43" s="12">
+        <v>83</v>
+      </c>
+      <c r="G43" s="12">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>81</v>
+      </c>
+      <c r="F44" s="12">
+        <v>83</v>
+      </c>
+      <c r="G44" s="12">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>81</v>
+      </c>
+      <c r="F45" s="12">
+        <v>83</v>
+      </c>
+      <c r="G45" s="12">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -5047,19 +5742,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F1A6FD-F375-4FB8-8C30-C4A005067594}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5082,7 +5777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5105,7 +5800,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5128,7 +5823,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5151,7 +5846,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5174,7 +5869,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5197,7 +5892,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5220,7 +5915,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5243,7 +5938,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5266,7 +5961,7 @@
         <v>41.6</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5289,7 +5984,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5312,7 +6007,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5335,7 +6030,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5358,7 +6053,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5381,7 +6076,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5404,7 +6099,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5427,7 +6122,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5450,7 +6145,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5473,7 +6168,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5496,7 +6191,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5519,7 +6214,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5542,7 +6237,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5565,7 +6260,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5588,7 +6283,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5611,7 +6306,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -5634,7 +6329,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -5657,7 +6352,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -5680,7 +6375,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -5703,7 +6398,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -5726,7 +6421,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -5749,7 +6444,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -5772,7 +6467,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -5795,7 +6490,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -5818,7 +6513,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -5841,7 +6536,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -5864,7 +6559,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5887,7 +6582,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5910,7 +6605,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5933,7 +6628,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5954,6 +6649,144 @@
       </c>
       <c r="G39" s="14">
         <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="14">
+        <v>129</v>
+      </c>
+      <c r="F40" s="14">
+        <v>131</v>
+      </c>
+      <c r="G40" s="14">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="14">
+        <v>124</v>
+      </c>
+      <c r="F41" s="14">
+        <v>126</v>
+      </c>
+      <c r="G41" s="14">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="14">
+        <v>123</v>
+      </c>
+      <c r="F42" s="14">
+        <v>125</v>
+      </c>
+      <c r="G42" s="14">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="14">
+        <v>123</v>
+      </c>
+      <c r="F43" s="14">
+        <v>125</v>
+      </c>
+      <c r="G43" s="14">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="14">
+        <v>123</v>
+      </c>
+      <c r="F44" s="14">
+        <v>125</v>
+      </c>
+      <c r="G44" s="14">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="14">
+        <v>123</v>
+      </c>
+      <c r="F45" s="14">
+        <v>125</v>
+      </c>
+      <c r="G45" s="14">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -5964,19 +6797,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F720D88E-37F2-4EF2-B2CA-01688ACF7295}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5999,7 +6832,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6022,7 +6855,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6045,7 +6878,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6068,7 +6901,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6091,7 +6924,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6114,7 +6947,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6137,7 +6970,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6160,7 +6993,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6183,7 +7016,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6206,7 +7039,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6229,7 +7062,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6252,7 +7085,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6275,7 +7108,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6298,7 +7131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -6321,7 +7154,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -6344,7 +7177,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -6367,7 +7200,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -6390,7 +7223,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -6413,7 +7246,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -6436,7 +7269,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -6459,7 +7292,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -6482,7 +7315,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -6505,7 +7338,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -6528,7 +7361,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6551,7 +7384,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6574,7 +7407,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6597,7 +7430,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6620,7 +7453,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6643,7 +7476,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6666,7 +7499,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6689,7 +7522,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6712,7 +7545,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6735,7 +7568,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6758,7 +7591,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6781,7 +7614,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6804,7 +7637,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6827,7 +7660,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6850,7 +7683,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6871,6 +7704,144 @@
       </c>
       <c r="G39" s="12">
         <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="12">
+        <v>87</v>
+      </c>
+      <c r="F40" s="12">
+        <v>89</v>
+      </c>
+      <c r="G40" s="12">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="12">
+        <v>84</v>
+      </c>
+      <c r="F41" s="12">
+        <v>87</v>
+      </c>
+      <c r="G41" s="12">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="12">
+        <v>83</v>
+      </c>
+      <c r="F42" s="12">
+        <v>86</v>
+      </c>
+      <c r="G42" s="12">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="12">
+        <v>83</v>
+      </c>
+      <c r="F43" s="12">
+        <v>86</v>
+      </c>
+      <c r="G43" s="12">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="12">
+        <v>83</v>
+      </c>
+      <c r="F44" s="12">
+        <v>86</v>
+      </c>
+      <c r="G44" s="12">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="12">
+        <v>83</v>
+      </c>
+      <c r="F45" s="12">
+        <v>86</v>
+      </c>
+      <c r="G45" s="12">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -6881,19 +7852,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD5A656-5B30-45CF-B579-A97C69E643A5}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="16"/>
+    <col min="7" max="7" width="11.21875" style="16" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6906,17 +7877,17 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6929,17 +7900,17 @@
       <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="16">
         <v>44</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="16">
         <v>46</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6952,17 +7923,17 @@
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="16">
         <v>44</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="16">
         <v>46</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6975,17 +7946,17 @@
       <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="16">
         <v>44</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="16">
         <v>46</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6998,17 +7969,17 @@
       <c r="D5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="16">
         <v>44</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="16">
         <v>46</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -7021,17 +7992,17 @@
       <c r="D6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="16">
         <v>44</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="16">
         <v>46</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -7044,17 +8015,17 @@
       <c r="D7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="16">
         <v>44</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="16">
         <v>46</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -7067,17 +8038,17 @@
       <c r="D8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="16">
         <v>44</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="16">
         <v>46</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -7090,17 +8061,17 @@
       <c r="D9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="16">
         <v>44</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="16">
         <v>46</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="16">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -7113,17 +8084,17 @@
       <c r="D10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="16">
         <v>44.3</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="16">
         <v>46.3</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="16">
         <v>45.3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -7136,17 +8107,17 @@
       <c r="D11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="16">
         <v>44.3</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="16">
         <v>46.3</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="16">
         <v>45.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -7159,17 +8130,17 @@
       <c r="D12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="16">
         <v>44.3</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="16">
         <v>46.3</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="16">
         <v>45.3</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -7182,17 +8153,17 @@
       <c r="D13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="16">
         <v>53</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="16">
         <v>55</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="16">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -7205,17 +8176,17 @@
       <c r="D14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="16">
         <v>53</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="16">
         <v>55</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="16">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -7228,17 +8199,17 @@
       <c r="D15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="16">
         <v>62</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="16">
         <v>64</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="16">
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7251,17 +8222,17 @@
       <c r="D16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="16">
         <v>62</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="16">
         <v>64</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="16">
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7274,17 +8245,17 @@
       <c r="D17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="16">
         <v>62</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="16">
         <v>64</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="16">
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7297,17 +8268,17 @@
       <c r="D18" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="16">
         <v>62</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="16">
         <v>64</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="16">
         <v>63</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7320,17 +8291,17 @@
       <c r="D19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="16">
         <v>79</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="16">
         <v>81</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="16">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7343,17 +8314,17 @@
       <c r="D20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="16">
         <v>99</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="16">
         <v>101</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="16">
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7366,17 +8337,17 @@
       <c r="D21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="16">
         <v>109</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="16">
         <v>111</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="16">
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7389,17 +8360,17 @@
       <c r="D22" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="16">
         <v>109</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="16">
         <v>111</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="16">
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7412,17 +8383,17 @@
       <c r="D23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="16">
         <v>109</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="16">
         <v>111</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="16">
         <v>110</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7435,17 +8406,17 @@
       <c r="D24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="16">
         <v>109</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="16">
         <v>111</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="16">
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7458,17 +8429,17 @@
       <c r="D25" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="16">
         <v>114</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="16">
         <v>116</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="16">
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -7481,17 +8452,17 @@
       <c r="D26" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="16">
         <v>114</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="16">
         <v>116</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="16">
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -7504,17 +8475,17 @@
       <c r="D27" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="16">
         <v>129</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="16">
         <v>131</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="16">
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -7527,17 +8498,17 @@
       <c r="D28" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="16">
         <v>144</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="16">
         <v>146</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="16">
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -7550,17 +8521,17 @@
       <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="16">
         <v>144</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="16">
         <v>146</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="16">
         <v>145</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -7573,17 +8544,17 @@
       <c r="D30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="16">
         <v>144</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="16">
         <v>146</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="16">
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -7596,17 +8567,17 @@
       <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="16">
         <v>144</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="16">
         <v>146</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="16">
         <v>145</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -7619,17 +8590,17 @@
       <c r="D32" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="16">
         <v>144</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="16">
         <v>146</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="16">
         <v>145</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -7642,17 +8613,17 @@
       <c r="D33" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="16">
         <v>169</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="16">
         <v>171</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="16">
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -7665,17 +8636,17 @@
       <c r="D34" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="16">
         <v>169</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="16">
         <v>171</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="16">
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -7688,17 +8659,17 @@
       <c r="D35" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="16">
         <v>169</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="16">
         <v>171</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="16">
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -7711,17 +8682,17 @@
       <c r="D36" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="16">
         <v>164</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="16">
         <v>166</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="16">
         <v>165</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -7734,17 +8705,17 @@
       <c r="D37" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="16">
         <v>164</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="16">
         <v>166</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="16">
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -7757,17 +8728,17 @@
       <c r="D38" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="16">
         <v>159</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="16">
         <v>161</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="16">
         <v>160</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -7780,14 +8751,152 @@
       <c r="D39" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="16">
         <v>155</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="16">
         <v>157</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="16">
         <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="16">
+        <v>143</v>
+      </c>
+      <c r="F40" s="16">
+        <v>146</v>
+      </c>
+      <c r="G40" s="16">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="16">
+        <v>138</v>
+      </c>
+      <c r="F41" s="16">
+        <v>141</v>
+      </c>
+      <c r="G41" s="16">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="16">
+        <v>138</v>
+      </c>
+      <c r="F42" s="16">
+        <v>141</v>
+      </c>
+      <c r="G42" s="16">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="16">
+        <v>138</v>
+      </c>
+      <c r="F43" s="16">
+        <v>141</v>
+      </c>
+      <c r="G43" s="16">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="16">
+        <v>138</v>
+      </c>
+      <c r="F44" s="16">
+        <v>141</v>
+      </c>
+      <c r="G44" s="16">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="16">
+        <v>138</v>
+      </c>
+      <c r="F45" s="16">
+        <v>141</v>
+      </c>
+      <c r="G45" s="16">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -7798,19 +8907,19 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3EDF89-A497-4D9B-AE60-D1EDE4F7FB0B}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.19921875" style="12" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="16"/>
+    <col min="7" max="7" width="11.21875" style="16" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7823,17 +8932,17 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -7846,17 +8955,17 @@
       <c r="D2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="16">
         <v>80</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="16">
         <v>87</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -7869,17 +8978,17 @@
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="16">
         <v>80</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="16">
         <v>87</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -7892,17 +9001,17 @@
       <c r="D4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="16">
         <v>80</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="16">
         <v>87</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -7915,17 +9024,17 @@
       <c r="D5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="16">
         <v>80</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="16">
         <v>87</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -7938,17 +9047,17 @@
       <c r="D6" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="16">
         <v>80</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="16">
         <v>87</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -7961,17 +9070,17 @@
       <c r="D7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="16">
         <v>80</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="16">
         <v>87</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -7984,17 +9093,17 @@
       <c r="D8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="16">
         <v>80</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="16">
         <v>87</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -8007,17 +9116,17 @@
       <c r="D9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="16">
         <v>80</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="16">
         <v>87</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="16">
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -8030,17 +9139,17 @@
       <c r="D10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="16">
         <v>80.2</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="16">
         <v>87.2</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="16">
         <v>83.2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -8053,17 +9162,17 @@
       <c r="D11" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="16">
         <v>80.2</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="16">
         <v>87.2</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="16">
         <v>83.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -8076,17 +9185,17 @@
       <c r="D12" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="16">
         <v>80.2</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="16">
         <v>87.2</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="16">
         <v>83.2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -8099,17 +9208,17 @@
       <c r="D13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="16">
         <v>95</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="16">
         <v>102</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="16">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -8122,17 +9231,17 @@
       <c r="D14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="16">
         <v>95</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="16">
         <v>102</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="16">
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -8145,17 +9254,17 @@
       <c r="D15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="16">
         <v>112</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="16">
         <v>119</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="16">
         <v>115</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -8168,17 +9277,17 @@
       <c r="D16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="16">
         <v>112</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="16">
         <v>119</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="16">
         <v>115</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -8191,17 +9300,17 @@
       <c r="D17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="16">
         <v>112</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="16">
         <v>119</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="16">
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -8214,17 +9323,17 @@
       <c r="D18" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="16">
         <v>112</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="16">
         <v>119</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="16">
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -8237,17 +9346,17 @@
       <c r="D19" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="16">
         <v>147</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="16">
         <v>154</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="16">
         <v>150</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -8260,17 +9369,17 @@
       <c r="D20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="16">
         <v>197</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="16">
         <v>204</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="16">
         <v>200</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -8283,17 +9392,17 @@
       <c r="D21" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="16">
         <v>217</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="16">
         <v>224</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="16">
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -8306,17 +9415,17 @@
       <c r="D22" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="16">
         <v>217</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="16">
         <v>224</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="16">
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -8329,17 +9438,17 @@
       <c r="D23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="16">
         <v>217</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="16">
         <v>224</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="16">
         <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -8352,17 +9461,17 @@
       <c r="D24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="16">
         <v>217</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="16">
         <v>224</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="16">
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -8375,17 +9484,17 @@
       <c r="D25" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="16">
         <v>232</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="16">
         <v>239</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="16">
         <v>235</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -8398,17 +9507,17 @@
       <c r="D26" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="16">
         <v>232</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="16">
         <v>239</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="16">
         <v>235</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -8421,17 +9530,17 @@
       <c r="D27" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="16">
         <v>247</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="16">
         <v>254</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="16">
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -8444,17 +9553,17 @@
       <c r="D28" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="16">
         <v>257</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="16">
         <v>264</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="16">
         <v>260</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -8467,17 +9576,17 @@
       <c r="D29" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="16">
         <v>257</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="16">
         <v>264</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="16">
         <v>260</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -8490,17 +9599,17 @@
       <c r="D30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E30" s="12">
+      <c r="E30" s="16">
         <v>257</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="16">
         <v>264</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="16">
         <v>260</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -8513,17 +9622,17 @@
       <c r="D31" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="12">
+      <c r="E31" s="16">
         <v>257</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="16">
         <v>264</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="16">
         <v>260</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -8536,17 +9645,17 @@
       <c r="D32" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="16">
         <v>257</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="16">
         <v>264</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="16">
         <v>260</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -8559,17 +9668,17 @@
       <c r="D33" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E33" s="12">
+      <c r="E33" s="16">
         <v>297</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="16">
         <v>304</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="16">
         <v>300</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -8582,17 +9691,17 @@
       <c r="D34" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="16">
         <v>297</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="16">
         <v>304</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="16">
         <v>300</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -8605,17 +9714,17 @@
       <c r="D35" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E35" s="16">
         <v>297</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="16">
         <v>304</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="16">
         <v>300</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -8628,17 +9737,17 @@
       <c r="D36" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="12">
+      <c r="E36" s="16">
         <v>292</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="16">
         <v>299</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="16">
         <v>295</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -8651,17 +9760,17 @@
       <c r="D37" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="12">
+      <c r="E37" s="16">
         <v>292</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="16">
         <v>299</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="16">
         <v>295</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -8674,17 +9783,17 @@
       <c r="D38" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E38" s="16">
         <v>287</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="16">
         <v>294</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="16">
         <v>290</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -8697,14 +9806,152 @@
       <c r="D39" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E39" s="12">
+      <c r="E39" s="16">
         <v>277</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="16">
         <v>284</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="16">
         <v>280</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="16">
+        <v>267</v>
+      </c>
+      <c r="F40" s="16">
+        <v>274</v>
+      </c>
+      <c r="G40" s="16">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="16">
+        <v>262</v>
+      </c>
+      <c r="F41" s="16">
+        <v>269</v>
+      </c>
+      <c r="G41" s="16">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="16">
+        <v>257</v>
+      </c>
+      <c r="F42" s="16">
+        <v>264</v>
+      </c>
+      <c r="G42" s="16">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="16">
+        <v>257</v>
+      </c>
+      <c r="F43" s="16">
+        <v>264</v>
+      </c>
+      <c r="G43" s="16">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="16">
+        <v>257</v>
+      </c>
+      <c r="F44" s="16">
+        <v>264</v>
+      </c>
+      <c r="G44" s="16">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="16">
+        <v>257</v>
+      </c>
+      <c r="F45" s="16">
+        <v>264</v>
+      </c>
+      <c r="G45" s="16">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
